--- a/forms/trg/Formulir_TRG_dtdds.xlsx
+++ b/forms/trg/Formulir_TRG_dtdds.xlsx
@@ -918,7 +918,7 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>LEADER</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>LECTURERS</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -988,7 +988,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>LECTURERS</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>LECTURERS</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="12" t="n"/>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="12" t="n"/>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D22" s="12" t="n"/>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D23" s="12" t="n"/>
